--- a/artfynd/A 15728-2026 artfynd.xlsx
+++ b/artfynd/A 15728-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132286808</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132286762</v>
+        <v>132287626</v>
       </c>
       <c r="B3" t="n">
-        <v>58328</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,51 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Frimanssved, Nälden, Näskott, Jmt</t>
+          <t>Frimanssved, Frimanssved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464353</v>
+        <v>464385</v>
       </c>
       <c r="R3" t="n">
-        <v>7023607</v>
+        <v>7023624</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bedagade fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132287443</v>
+        <v>132287985</v>
       </c>
       <c r="B4" t="n">
-        <v>57954</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464400</v>
+        <v>464339</v>
       </c>
       <c r="R4" t="n">
-        <v>7023560</v>
+        <v>7023629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barkfläkt klen gran</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,45 +1011,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132287626</v>
+        <v>132286780</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Frimanssved, Frimanssved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464385</v>
+        <v>464352</v>
       </c>
       <c r="R5" t="n">
-        <v>7023624</v>
+        <v>7023607</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bedagade fruktkroppar</t>
+          <t>Barkfläkta granar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132287692</v>
+        <v>132287034</v>
       </c>
       <c r="B6" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464386</v>
+        <v>464400</v>
       </c>
       <c r="R6" t="n">
-        <v>7023630</v>
+        <v>7023560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Barkfläkt klen gran</t>
+          <t>Barkfläkt gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132286780</v>
+        <v>132287692</v>
       </c>
       <c r="B7" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,19 +1276,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Frimanssved, Frimanssved, Jmt</t>
+          <t>Frimanssved, Nälden, Näskott, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464352</v>
+        <v>464386</v>
       </c>
       <c r="R7" t="n">
-        <v>7023607</v>
+        <v>7023630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Barkfläkta granar</t>
+          <t>Barkfläkt klen gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,27 +1362,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132287985</v>
+        <v>132286762</v>
       </c>
       <c r="B8" t="n">
-        <v>57951</v>
+        <v>58349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1399,10 +1390,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464339</v>
+        <v>464353</v>
       </c>
       <c r="R8" t="n">
-        <v>7023629</v>
+        <v>7023607</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
